--- a/output/pdf_financials_xlsx/WRUN.xlsx
+++ b/output/pdf_financials_xlsx/WRUN.xlsx
@@ -3065,7 +3065,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>0.022162</v>
       </c>

--- a/output/pdf_financials_xlsx/WRUN.xlsx
+++ b/output/pdf_financials_xlsx/WRUN.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-1.3e-05</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.346681</v>
+        <v>-1.346668</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-4.161416</v>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.346681</v>
+        <v>-1.346668</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-4.161416</v>
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.623789</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.203808</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.011111</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.623789</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.203808</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.011111</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.659477</v>
+        <v>0.035688</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.221077</v>
+        <v>0.017269</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.032131</v>
+        <v>0.02102</v>
       </c>
     </row>
     <row r="49">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">

--- a/output/pdf_financials_xlsx/WRUN.xlsx
+++ b/output/pdf_financials_xlsx/WRUN.xlsx
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.037866</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -4194,7 +4194,11 @@
           <t>Proceeds from disposal of investments</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>0.037866</v>
       </c>
